--- a/data/Ascona/cost/total_demand.xlsx
+++ b/data/Ascona/cost/total_demand.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1098832.088351694</v>
+        <v>1099913.243169348</v>
       </c>
     </row>
   </sheetData>
